--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="84">
   <si>
     <t>Profile</t>
   </si>
@@ -50,7 +50,7 @@
     <t>mii-pr-mikrobio-allgemeine-bestimmung</t>
   </si>
   <si>
-    <t>MII PR Mikrobio Allgemeine Bestimmung</t>
+    <t>MII PR Mikrobio Allgemeine Bestimmung (Identifizierung)</t>
   </si>
   <si>
     <t>null#laboratory, null#MB</t>
@@ -59,7 +59,10 @@
     <t/>
   </si>
   <si>
-    <t>LOINC#41852-5, LOINC#null</t>
+    <t>null#null</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-allgemeine-bestimmung-tests-loinc (extensible)</t>
   </si>
   <si>
     <t>dateTimeĵ</t>
@@ -77,7 +80,7 @@
     <t>MII PR Mikrobio Allgemeine Kultur</t>
   </si>
   <si>
-    <t>LOINC#11475-1, LOINC#null</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-allgemeine-kultur-tests-loinc (extensible)</t>
   </si>
   <si>
     <t>mii-pr-mikrobio-antigen-antikoerper-quantitativ</t>
@@ -86,9 +89,6 @@
     <t>MII PR Mikrobio Antigen Antikoerper Quantitativ</t>
   </si>
   <si>
-    <t>null#null</t>
-  </si>
-  <si>
     <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-antigen-antikoerper-quantitative-tests-loinc (extensible)</t>
   </si>
   <si>
@@ -104,10 +104,10 @@
     <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-aviditaet-tests-loinc (extensible)</t>
   </si>
   <si>
-    <t>mii-pr-mikrobio-barlett-score</t>
-  </si>
-  <si>
-    <t>MII PR Mikrobio Barlett Score</t>
+    <t>mii-pr-mikrobio-bartlett-score</t>
+  </si>
+  <si>
+    <t>MII PR Mikrobio Bartlett Score</t>
   </si>
   <si>
     <t>LOINC#75371-5, LOINC#null</t>
@@ -152,10 +152,16 @@
     <t>mii-pr-mikrobio-mikroskopie</t>
   </si>
   <si>
-    <t>MII PR Mikrobio Mikroskopie</t>
-  </si>
-  <si>
-    <t>LOINC#105059-0, LOINC#null</t>
+    <t>MII PR Mikrobio Allgemeine Mikroskopie</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-allgemeine-mikroskopie-tests-loinc (extensible)</t>
+  </si>
+  <si>
+    <t>MII CS Mikrobio Mikroskopie Komponenten#semiquantitative-menge</t>
+  </si>
+  <si>
+    <t>CodeableConcept</t>
   </si>
   <si>
     <t>mii-pr-mikrobio-molekulare-pathogenlast</t>
@@ -219,6 +225,15 @@
   </si>
   <si>
     <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-spezifische-kultur-tests-loinc (extensible)</t>
+  </si>
+  <si>
+    <t>mii-pr-mikrobio-spezifische-mikroskopie</t>
+  </si>
+  <si>
+    <t>MII PR Mikrobio Spezifische Mikroskopie</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-spezifische-mikroskopie-tests-loinc (extensible)</t>
   </si>
   <si>
     <t>mii-pr-mikrobio-titer</t>
@@ -382,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -437,16 +452,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s" s="2">
         <v>14</v>
@@ -457,10 +472,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>13</v>
@@ -469,19 +484,19 @@
         <v>14</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" t="s" s="2">
         <v>14</v>
@@ -492,10 +507,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>13</v>
@@ -504,19 +519,19 @@
         <v>14</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s" s="2">
         <v>25</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>26</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" t="s" s="2">
         <v>14</v>
@@ -539,19 +554,19 @@
         <v>14</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s" s="2">
         <v>29</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>26</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s" s="2">
         <v>14</v>
@@ -580,13 +595,13 @@
         <v>14</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s" s="2">
         <v>14</v>
@@ -609,19 +624,19 @@
         <v>14</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>26</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" t="s" s="2">
         <v>14</v>
@@ -644,19 +659,19 @@
         <v>14</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>40</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>26</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" t="s" s="2">
         <v>14</v>
@@ -679,19 +694,19 @@
         <v>14</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>43</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>26</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9" t="s" s="2">
         <v>14</v>
@@ -714,19 +729,19 @@
         <v>14</v>
       </c>
       <c r="E10" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="F10" t="s" s="2">
-        <v>14</v>
-      </c>
       <c r="G10" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>14</v>
@@ -737,31 +752,31 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="F11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H11" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="C11" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F11" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="G11" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H11" t="s" s="2">
-        <v>26</v>
-      </c>
       <c r="I11" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>14</v>
@@ -772,31 +787,31 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="B12" t="s" s="2">
+      <c r="C12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="C12" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="F12" t="s" s="2">
-        <v>14</v>
-      </c>
       <c r="G12" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>14</v>
@@ -807,101 +822,101 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="B13" t="s" s="2">
+      <c r="C13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="C13" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>56</v>
-      </c>
       <c r="F13" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>14</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="B14" t="s" s="2">
+      <c r="C14" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="C14" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>24</v>
-      </c>
       <c r="F14" t="s" s="2">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>14</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="B15" t="s" s="2">
+      <c r="C15" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="C15" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E15" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F15" t="s" s="2">
-        <v>62</v>
-      </c>
       <c r="G15" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>14</v>
@@ -912,31 +927,31 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="B16" t="s" s="2">
+      <c r="C16" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="C16" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E16" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F16" t="s" s="2">
-        <v>65</v>
-      </c>
       <c r="G16" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>14</v>
@@ -947,31 +962,31 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="B17" t="s" s="2">
+      <c r="C17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F17" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="C17" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F17" t="s" s="2">
-        <v>68</v>
-      </c>
       <c r="G17" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>14</v>
@@ -982,31 +997,31 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="B18" t="s" s="2">
+      <c r="C18" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F18" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="C18" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E18" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F18" t="s" s="2">
-        <v>71</v>
-      </c>
       <c r="G18" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>14</v>
@@ -1017,31 +1032,31 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F19" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="B19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E19" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F19" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="G19" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>14</v>
@@ -1052,36 +1067,106 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F20" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="G20" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H20" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="C20" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F20" t="s" s="2">
+      <c r="I20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="G20" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="I20" t="s" s="2">
+      <c r="B21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H21" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="J20" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K20" t="s" s="2">
+      <c r="I21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K22" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="81">
   <si>
     <t>Profile</t>
   </si>
@@ -158,7 +158,7 @@
     <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-allgemeine-mikroskopie-tests-loinc (extensible)</t>
   </si>
   <si>
-    <t>MII CS Mikrobio Mikroskopie Komponenten#semiquantitative-menge</t>
+    <t>SNOMED CT#103392008</t>
   </si>
   <si>
     <t>CodeableConcept</t>
@@ -216,15 +216,6 @@
   </si>
   <si>
     <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-spezifische-bestimmung-tests-loinc (extensible)</t>
-  </si>
-  <si>
-    <t>mii-pr-mikrobio-spezifische-kultur</t>
-  </si>
-  <si>
-    <t>MII PR Mikrobio Spezifische Kultur</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-spezifische-kultur-tests-loinc (extensible)</t>
   </si>
   <si>
     <t>mii-pr-mikrobio-spezifische-mikroskopie</t>
@@ -397,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1018,7 +1009,7 @@
         <v>17</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>19</v>
@@ -1053,7 +1044,7 @@
         <v>17</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>19</v>
@@ -1067,10 +1058,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>13</v>
@@ -1082,13 +1073,13 @@
         <v>15</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>19</v>
@@ -1132,41 +1123,6 @@
         <v>14</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D22" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E22" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="F22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G22" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K22" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="81">
   <si>
     <t>Profile</t>
   </si>
@@ -161,7 +161,7 @@
     <t>SNOMED CT#103392008</t>
   </si>
   <si>
-    <t>CodeableConcept</t>
+    <t>Quantity, CodeableConcept, Range</t>
   </si>
   <si>
     <t>mii-pr-mikrobio-molekulare-pathogenlast</t>
@@ -388,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1009,7 +1009,7 @@
         <v>17</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>19</v>
@@ -1023,28 +1023,28 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>19</v>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>13</v>
@@ -1073,13 +1073,13 @@
         <v>15</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>19</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>13</v>
@@ -1108,7 +1108,7 @@
         <v>15</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>17</v>
@@ -1123,6 +1123,41 @@
         <v>14</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K22" t="s" s="2">
         <v>14</v>
       </c>
     </row>
